--- a/api/xlsx/en/HumanitarianGlobalClusters.xlsx
+++ b/api/xlsx/en/HumanitarianGlobalClusters.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="53">
   <si>
     <t>code</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>public-database</t>
   </si>
   <si>
     <t>4</t>
@@ -514,10 +517,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -536,215 +539,218 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/HumanitarianGlobalClusters.xlsx
+++ b/api/xlsx/en/HumanitarianGlobalClusters.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="52">
   <si>
     <t>code</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>status</t>
-  </si>
-  <si>
-    <t>public-database</t>
   </si>
   <si>
     <t>4</t>
@@ -517,10 +514,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -539,218 +536,215 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
+      <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
+      <c r="E6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
         <v>22</v>
       </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
         <v>25</v>
       </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
         <v>28</v>
       </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
+      <c r="E9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>31</v>
       </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="B10" t="s">
+      <c r="E10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
         <v>34</v>
       </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>35</v>
       </c>
-      <c r="B11" t="s">
+      <c r="E11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
         <v>37</v>
       </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>38</v>
       </c>
-      <c r="B12" t="s">
+      <c r="E12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
         <v>40</v>
       </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="B13" t="s">
+      <c r="E13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
         <v>43</v>
       </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>44</v>
       </c>
-      <c r="B14" t="s">
+      <c r="E14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
         <v>46</v>
       </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>47</v>
       </c>
-      <c r="B15" t="s">
+      <c r="E15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
         <v>49</v>
       </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>50</v>
       </c>
-      <c r="B16" t="s">
+      <c r="E16" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/HumanitarianGlobalClusters.xlsx
+++ b/api/xlsx/en/HumanitarianGlobalClusters.xlsx
@@ -14,18 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
   <si>
     <t>code</t>
   </si>
   <si>
     <t>name</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>category</t>
   </si>
   <si>
     <t>url</t>
@@ -514,10 +508,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -530,240 +524,234 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="B7" t="s">
         <v>21</v>
       </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="C7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="C8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="B9" t="s">
         <v>27</v>
       </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="C9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="B10" t="s">
         <v>30</v>
       </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+      <c r="C10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
+      <c r="C11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
+      <c r="C12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="B13" t="s">
         <v>39</v>
       </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
+      <c r="C13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B13" t="s">
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="B14" t="s">
         <v>42</v>
       </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
+      <c r="C14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="B15" t="s">
         <v>45</v>
       </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
+      <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="B16" t="s">
         <v>48</v>
       </c>
-      <c r="F15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
+      <c r="C16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
+      <c r="D16" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C5" r:id="rId4"/>
+    <hyperlink ref="C6" r:id="rId5"/>
+    <hyperlink ref="C7" r:id="rId6"/>
+    <hyperlink ref="C8" r:id="rId7"/>
+    <hyperlink ref="C9" r:id="rId8"/>
+    <hyperlink ref="C10" r:id="rId9"/>
+    <hyperlink ref="C11" r:id="rId10"/>
+    <hyperlink ref="C12" r:id="rId11"/>
+    <hyperlink ref="C13" r:id="rId12"/>
+    <hyperlink ref="C14" r:id="rId13"/>
+    <hyperlink ref="C15" r:id="rId14"/>
+    <hyperlink ref="C16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
